--- a/results/log_pv_inst/log_pv_inst_densities_fdensity_effects.xlsx
+++ b/results/log_pv_inst/log_pv_inst_densities_fdensity_effects.xlsx
@@ -511,7 +511,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>fdensity</t>
+          <t>D(Firms)</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -608,7 +608,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>log_income</t>
+          <t>Income</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -705,7 +705,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>log_hholds</t>
+          <t>Households</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -802,7 +802,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>log_sunny_hours</t>
+          <t>Sunny hours</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
